--- a/Assets/Resources/DataFiles/CharData/ExcelFile/StatDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/ExcelFile/StatDataLabel.xlsx
@@ -1,14 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KOR" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ENG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,12 +32,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +57,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -854,4 +867,448 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>statKey</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>maxHealth</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>最大HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>maxMana</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>最大MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>attackPower</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>攻撃力</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>defensePower</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>防御力</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>critRate</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>クリティカル率</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>critMult</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>クリティカルダメージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>移動速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>attackSpeed</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>攻撃速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>cdr</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>スキルクールタイム減少</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>mpRegen</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>マナ回復力</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>貫通力</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>skillRange</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>スキル範囲増加</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>fireBonus</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>火属性ダメージボーナス</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>iceBonus</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>氷属性ダメージボーナス</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>electricBonus</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>電気属性ダメージボーナス</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>statKey</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>maxHealth</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>最大HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>maxMana</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>最大MP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>attackPower</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>defensePower</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>防御力</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>critRate</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>暴击率</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>critMult</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>暴击伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>移动速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>attackSpeed</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>攻击速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>cdr</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>技能冷却缩减</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>mpRegen</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>魔力回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>穿透力</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>skillRange</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>技能范围提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>fireBonus</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>火属性伤害加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>iceBonus</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>冰属性伤害加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>electricBonus</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>电属性伤害加成</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>